--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_otrasrel_a_2018_la_araucania.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_otrasrel_a_2018_la_araucania.xlsx
@@ -120,7 +120,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 13:47</t>
+    <t xml:space="preserve">2026-09-24 00:38</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -558,7 +558,7 @@
         <v>-0.58</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>-0.58</v>
@@ -604,10 +604,10 @@
         <v>-0.56</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-0.04</v>
+        <v>-0.03</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>-0.52</v>
+        <v>-0.53</v>
       </c>
     </row>
     <row r="5">
@@ -673,10 +673,10 @@
         <v>-0.51</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.16</v>
+        <v>0.13</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>-0.67</v>
+        <v>-0.64</v>
       </c>
     </row>
     <row r="8">
@@ -696,10 +696,10 @@
         <v>0.06</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.16</v>
+        <v>0.13</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>-0.1</v>
+        <v>-0.07</v>
       </c>
     </row>
     <row r="9">
@@ -719,10 +719,10 @@
         <v>0.09</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0.23</v>
+        <v>0.2</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>-0.14</v>
+        <v>-0.11</v>
       </c>
     </row>
     <row r="10">
@@ -745,7 +745,7 @@
         <v>0.15</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>-0.51</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="11">
@@ -765,10 +765,10 @@
         <v>-0.36</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>-0.51</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="12">
@@ -788,10 +788,10 @@
         <v>-0.03</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>-0.05</v>
+        <v>-0.07</v>
       </c>
     </row>
     <row r="13">
@@ -811,10 +811,10 @@
         <v>0.17</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>0.13</v>
+        <v>0.15</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="14">
@@ -834,7 +834,7 @@
         <v>-0.27</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-0.18</v>
+        <v>-0.19</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>-0.08</v>
@@ -860,7 +860,7 @@
         <v>-0.06</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>-0.32</v>
+        <v>-0.33</v>
       </c>
     </row>
     <row r="16">
@@ -903,10 +903,10 @@
         <v>-0.7</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>-0.28</v>
+        <v>-0.27</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>-0.42</v>
+        <v>-0.43</v>
       </c>
     </row>
     <row r="18">
@@ -1090,7 +1090,7 @@
         <v>-0.06</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1179,10 +1179,10 @@
         <v>0.26</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>0.06</v>
+        <v>0.07</v>
       </c>
     </row>
     <row r="30">
@@ -1202,7 +1202,7 @@
         <v>0.21</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="G30" s="2" t="n">
         <v>0.04</v>
@@ -1248,7 +1248,7 @@
         <v>-0.14</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>-0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="G32" s="2" t="n">
         <v>-0.13</v>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_otrasrel_a_2018_la_araucania.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_otrasrel_a_2018_la_araucania.xlsx
@@ -120,7 +120,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:38</t>
+    <t xml:space="preserve">2026-10-01 23:11</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_otrasrel_a_2018_la_araucania.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_otrasrel_a_2018_la_araucania.xlsx
@@ -120,7 +120,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:11</t>
+    <t xml:space="preserve">2026-10-05 19:27</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
